--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484068_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484068_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.167</v>
+        <v>2.3684</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5539</v>
+        <v>1.1481</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6131</v>
+        <v>1.2203</v>
       </c>
       <c r="G2" t="n">
         <v>-2.3013</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>2.969</v>
+        <v>1.1705</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5281</v>
+        <v>1.1224</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4409</v>
+        <v>0.0481</v>
       </c>
       <c r="V2" t="n">
         <v>1.7137</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6973</v>
+        <v>1.1803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0871</v>
+        <v>-0.5421</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6102</v>
+        <v>1.7224</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4404</v>
@@ -688,13 +688,13 @@
         <v>2.579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9591</v>
+        <v>0.4422</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3095</v>
+        <v>0.6803</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3504</v>
+        <v>-0.2382</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4085</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1572</v>
+        <v>1.0863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4442</v>
+        <v>-0.6711</v>
       </c>
       <c r="F4" t="n">
-        <v>0.713</v>
+        <v>1.7574</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4169</v>
+        <v>0.1233</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0635</v>
+        <v>0.2969</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6465</v>
+        <v>-0.1736</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.592</v>
+        <v>-0.6372</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3551</v>
+        <v>0.0806</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7631</v>
+        <v>-0.7178</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1751</v>
+        <v>0.7604</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2916</v>
+        <v>0.2163</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1165</v>
+        <v>0.5442</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3838</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5557</v>
+        <v>-0.0339</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1718</v>
+        <v>-0.0298</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3619</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4724</v>
+        <v>-0.3619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1084</v>
+        <v>0.806</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9039</v>
+        <v>0.121</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0123</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.175</v>
+        <v>-0.4169</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.302</v>
+        <v>-1.0635</v>
       </c>
       <c r="I5" t="n">
-        <v>0.127</v>
+        <v>0.6465</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.592</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4849</v>
+        <v>-1.3551</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5597</v>
+        <v>0.7631</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1002</v>
+        <v>0.1751</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7869</v>
+        <v>0.2916</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6867</v>
+        <v>-0.1165</v>
       </c>
       <c r="P5" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-3.9677</v>
-      </c>
       <c r="R5" t="n">
-        <v>2.9758</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7681</v>
+        <v>0.0326</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0034</v>
+        <v>0.2325</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2353</v>
+        <v>-0.1999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5073</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1352</v>
+        <v>1.4724</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6279</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0011</v>
+        <v>0.6001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4476</v>
+        <v>-1.5525</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4488</v>
+        <v>2.1526</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1233</v>
+        <v>-0.175</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2969</v>
+        <v>-0.302</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1736</v>
+        <v>0.127</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6372</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0806</v>
+        <v>0.4849</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7178</v>
+        <v>-0.5597</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7604</v>
+        <v>-0.1002</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2163</v>
+        <v>-0.7869</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5442</v>
+        <v>0.6867</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>2.9758</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1489</v>
+        <v>1.2598</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8105</v>
+        <v>1.3548</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3384</v>
+        <v>-0.095</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3619</v>
+        <v>0.5073</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1352</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3619</v>
+        <v>-0.6279</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9583</v>
+        <v>-0.1653</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8144</v>
+        <v>-1.0776</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8562</v>
+        <v>0.9123</v>
       </c>
       <c r="G7" t="n">
         <v>0.5306</v>
@@ -1000,13 +1000,13 @@
         <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6711</v>
+        <v>0.1219</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.0509</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1167</v>
+        <v>0.1728</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8097</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4333</v>
+        <v>-2.5199</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7632</v>
+        <v>-3.6815</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.1617</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7163</v>
@@ -1078,13 +1078,13 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6959</v>
+        <v>0.6093</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2414</v>
+        <v>0.3232</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4545</v>
+        <v>0.2862</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SERRA CASTILLO</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.8127</v>
+        <v>-4.8672</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.1002</v>
+        <v>-4.9277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2875</v>
+        <v>0.0605</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.3386</v>
+        <v>-5.7924</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.044</v>
+        <v>-1.6787</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2946</v>
+        <v>-4.1137</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.6206</v>
+        <v>-4.4857</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9801</v>
+        <v>-0.2165</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6405</v>
+        <v>-4.2692</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7181</v>
+        <v>-1.3067</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0639</v>
+        <v>-1.4622</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6542</v>
+        <v>0.1555</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7935</v>
+        <v>2.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1834</v>
+        <v>-0.0141</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7537</v>
+        <v>0.2325</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4297</v>
+        <v>-0.2467</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9157999999999999</v>
+        <v>-1.6397</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6498</v>
+        <v>-0.9651999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>J. SERRA CASTILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5285</v>
+        <v>-5.0033</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.6451</v>
+        <v>-5.4031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1166</v>
+        <v>0.3997</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.7924</v>
+        <v>-6.3386</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6787</v>
+        <v>-3.044</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.1137</v>
+        <v>-3.2946</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.4857</v>
+        <v>-4.6206</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2165</v>
+        <v>-1.9801</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.2692</v>
+        <v>-2.6405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3067</v>
+        <v>-1.7181</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4622</v>
+        <v>-1.0639</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1555</v>
+        <v>-0.6542</v>
       </c>
       <c r="P10" t="n">
-        <v>2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6755</v>
+        <v>-0.374</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4849</v>
+        <v>-0.0566</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1905</v>
+        <v>-0.3175</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6397</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9651999999999999</v>
+        <v>0.6498</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.0085</v>
+        <v>-7.5372</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4506</v>
+        <v>-4.8951</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5579</v>
+        <v>-2.6421</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8541</v>
@@ -1312,13 +1312,13 @@
         <v>2.7774</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5945</v>
+        <v>-0.1232</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2492</v>
+        <v>0.3062</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3453</v>
+        <v>-0.4295</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3534</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.6103</v>
+        <v>-14.0518</v>
       </c>
       <c r="E12" t="n">
-        <v>-23.0398</v>
+        <v>-21.4816</v>
       </c>
       <c r="F12" t="n">
-        <v>7.429800000000002</v>
+        <v>7.429799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-22.3811</v>
@@ -1390,13 +1390,13 @@
         <v>21.8224</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5025</v>
+        <v>3.0613</v>
       </c>
       <c r="T12" t="n">
-        <v>2.552</v>
+        <v>4.1105</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0493</v>
+        <v>-1.0495</v>
       </c>
       <c r="V12" t="n">
         <v>-5.6429</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5681</v>
+        <v>6.4558</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3754</v>
+        <v>2.1064</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1927</v>
+        <v>4.3494</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6435</v>
+        <v>4.4424</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0331</v>
+        <v>2.1764</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6104</v>
+        <v>2.266</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6442</v>
+        <v>1.4745</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6091</v>
+        <v>0.8669</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0351</v>
+        <v>0.6075</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2877</v>
+        <v>2.9679</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6422</v>
+        <v>1.3095</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6455</v>
+        <v>1.6585</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8371</v>
+        <v>-0.4833</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9953</v>
+        <v>-0.2776</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1582</v>
+        <v>-0.2056</v>
       </c>
       <c r="V13" t="n">
-        <v>1.881</v>
+        <v>3.8854</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2065</v>
+        <v>3.8854</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3239</v>
+        <v>5.6798</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0901</v>
+        <v>3.1594</v>
       </c>
       <c r="F14" t="n">
-        <v>6.414</v>
+        <v>2.5205</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6883</v>
+        <v>6.4904</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4264</v>
+        <v>4.2439</v>
       </c>
       <c r="I14" t="n">
-        <v>1.262</v>
+        <v>2.2465</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2189</v>
+        <v>4.1978</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0191</v>
+        <v>3.0656</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1997</v>
+        <v>1.1322</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9072</v>
+        <v>2.2926</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4455</v>
+        <v>1.1783</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4617</v>
+        <v>1.1143</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7664</v>
+        <v>-0.6122</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5726</v>
+        <v>-0.3286</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1938</v>
+        <v>-0.2836</v>
       </c>
       <c r="V14" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7384</v>
+        <v>1.4724</v>
       </c>
       <c r="X14" t="n">
         <v>-1.4724</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0283</v>
+        <v>5.054</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5963</v>
+        <v>1.5249</v>
       </c>
       <c r="F15" t="n">
-        <v>3.432</v>
+        <v>3.5291</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4424</v>
+        <v>7.3454</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1764</v>
+        <v>5.3074</v>
       </c>
       <c r="I15" t="n">
-        <v>2.266</v>
+        <v>2.038</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4745</v>
+        <v>4.9151</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8669</v>
+        <v>3.5898</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6075</v>
+        <v>1.3253</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9679</v>
+        <v>2.4303</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3095</v>
+        <v>1.7176</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6585</v>
+        <v>0.7127</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3887</v>
+        <v>-2.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9758</v>
+        <v>-4.1661</v>
       </c>
       <c r="R15" t="n">
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9108</v>
+        <v>0.2876</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.2439</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.123</v>
+        <v>0.0437</v>
       </c>
       <c r="V15" t="n">
-        <v>3.8854</v>
+        <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8854</v>
+        <v>0.532</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7658</v>
+        <v>4.7186</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3208</v>
+        <v>-0.951</v>
       </c>
       <c r="F16" t="n">
-        <v>3.445</v>
+        <v>5.6696</v>
       </c>
       <c r="G16" t="n">
-        <v>7.3454</v>
+        <v>2.6435</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3074</v>
+        <v>1.0331</v>
       </c>
       <c r="I16" t="n">
-        <v>2.038</v>
+        <v>1.6104</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9151</v>
+        <v>-0.6442</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5898</v>
+        <v>-0.6091</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3253</v>
+        <v>-0.0351</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4303</v>
+        <v>3.2877</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7176</v>
+        <v>1.6422</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7127</v>
+        <v>1.6455</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.579</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1661</v>
+        <v>-2.1822</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.9876</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0398</v>
+        <v>0.669</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0404</v>
+        <v>0.3187</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>1.881</v>
       </c>
       <c r="W16" t="n">
-        <v>0.532</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.532</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4487</v>
+        <v>3.5989</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6492</v>
+        <v>-1.6002</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7995</v>
+        <v>5.1991</v>
       </c>
       <c r="G17" t="n">
-        <v>6.4904</v>
+        <v>2.6883</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2439</v>
+        <v>1.4264</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2465</v>
+        <v>1.262</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1978</v>
+        <v>-1.2189</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0656</v>
+        <v>-0.0191</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1322</v>
+        <v>-1.1997</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2926</v>
+        <v>3.9072</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1783</v>
+        <v>1.4455</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1143</v>
+        <v>2.4617</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8433</v>
+        <v>1.0414</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8388</v>
+        <v>0.0625</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0045</v>
+        <v>0.9789</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4724</v>
+        <v>1.7384</v>
       </c>
       <c r="X17" t="n">
         <v>-1.4724</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1867</v>
+        <v>1.5727</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2756</v>
+        <v>0.0305</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4622</v>
+        <v>1.5422</v>
       </c>
       <c r="G18" t="n">
         <v>2.731</v>
@@ -1858,13 +1858,13 @@
         <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6156</v>
+        <v>-0.2296</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3117</v>
+        <v>-0.0056</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3039</v>
+        <v>-0.224</v>
       </c>
       <c r="V18" t="n">
         <v>-0.532</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0224</v>
+        <v>-1.2265</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9435</v>
+        <v>-2.1476</v>
       </c>
       <c r="F20" t="n">
         <v>0.9211</v>
@@ -2014,10 +2014,10 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6065</v>
+        <v>0.4024</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5669</v>
+        <v>0.3628</v>
       </c>
       <c r="U20" t="n">
         <v>0.0396</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7075</v>
+        <v>-1.5112</v>
       </c>
       <c r="E21" t="n">
         <v>-2.1778</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4703</v>
+        <v>0.6667</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7875</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3168</v>
+        <v>-0.1205</v>
       </c>
       <c r="T21" t="n">
         <v>0.4422</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.759</v>
+        <v>-0.5626</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3503</v>
+        <v>-3.0204</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.284</v>
+        <v>-1.978</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0662</v>
+        <v>-1.0424</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7819</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7154</v>
+        <v>-0.3855</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.289</v>
+        <v>0.0171</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4263</v>
+        <v>-0.4025</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6243</v>
+        <v>-3.3446</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7955</v>
+        <v>-4.5915</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1712</v>
+        <v>1.2469</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3475</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7772</v>
+        <v>-0.4975</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2153</v>
+        <v>-0.0113</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5619</v>
+        <v>-0.4862</v>
       </c>
       <c r="V23" t="n">
         <v>0.6745</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.6105</v>
+        <v>16.9706</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.4297</v>
+        <v>-7.429799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>23.0402</v>
+        <v>24.4006</v>
       </c>
       <c r="G24" t="n">
         <v>22.381</v>
@@ -2299,7 +2299,7 @@
         <v>7.5147</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6987</v>
+        <v>2.698700000000001</v>
       </c>
       <c r="K24" t="n">
         <v>4.1892</v>
@@ -2326,16 +2326,16 @@
         <v>10.9113</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5025</v>
+        <v>-0.1423999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0495</v>
+        <v>1.0497</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5519</v>
+        <v>-1.1917</v>
       </c>
       <c r="V24" t="n">
-        <v>5.642900000000001</v>
+        <v>5.6429</v>
       </c>
       <c r="W24" t="n">
         <v>10.6444</v>
